--- a/data/symbols.xlsx
+++ b/data/symbols.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\bourse\codal_monthly\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3D50BA4-1FE8-409F-89C9-EE01371E8354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7BC9FAE-CA55-43E7-A921-1359C5E3F30C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="14592" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="151">
   <si>
     <t>دتوزیع</t>
   </si>
@@ -469,6 +469,24 @@
   </si>
   <si>
     <t>دزهراوی</t>
+  </si>
+  <si>
+    <t>فسبزوار</t>
+  </si>
+  <si>
+    <t>جم پیلن</t>
+  </si>
+  <si>
+    <t>جم</t>
+  </si>
+  <si>
+    <t>شجم</t>
+  </si>
+  <si>
+    <t>نوری</t>
+  </si>
+  <si>
+    <t>غمایه</t>
   </si>
 </sst>
 </file>
@@ -786,7 +804,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A150"/>
+  <dimension ref="A1:A156"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.45">
@@ -1539,6 +1557,36 @@
         <v>144</v>
       </c>
     </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A151" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A152" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A153" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A154" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A155" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A156" t="s">
+        <v>150</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
